--- a/naver-place-crawler/results_health/기장군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/기장군_헬스장.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="Q2" t="n">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="R2" t="n">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q4" t="n">
         <v>604</v>
       </c>
       <c r="R4" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>강해짐 일광점 헬스&amp;PT</t>
+          <t>강해짐 정관점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -857,23 +857,23 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1357-1828</t>
+          <t>0507-1303-2889</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송4로 16 에코테라스 7층</t>
+          <t>부산광역시 기장군 정관읍 정관로 578 조은타워 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_AspkG</t>
+          <t>https://blog.naver.com/gang_hae_gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="Q5" t="n">
-        <v>368</v>
+        <v>330</v>
       </c>
       <c r="R5" t="n">
-        <v>552</v>
+        <v>664</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1142407899</t>
+          <t>1279713302</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142407899</t>
+          <t>https://m.place.naver.com/place/1279713302</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1094,10 @@
         <v>137</v>
       </c>
       <c r="Q7" t="n">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="R7" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
